--- a/content-templates/course-content-template.xlsx
+++ b/content-templates/course-content-template.xlsx
@@ -683,7 +683,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Complete: 0   Partial: 1   Minimal: 22</t>
+          <t>Complete: 0   Partial: 23   Minimal: 0</t>
         </is>
       </c>
     </row>
@@ -865,8 +865,16 @@
       </c>
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
-      <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to baking, covering Eggless Cake Sponge, Vanilla Sponge, Butterscotch Sponge, Chocolate Sponge, Mango Sponge and Strawberry Sponge, over a duration of 1 Month.</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Understand eggless cake sponge. | Learn to vanilla sponge. | Practice butterscotch sponge. | Explore chocolate sponge. | Use basic mango sponge. | Develop familiarity with strawberry sponge.</t>
+        </is>
+      </c>
       <c r="L2" s="9" t="n"/>
       <c r="M2" s="9" t="n"/>
       <c r="N2" s="9" t="n"/>
@@ -888,17 +896,17 @@
       <c r="R2" s="8" t="n"/>
       <c r="S2" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -940,8 +948,16 @@
       </c>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to nail art &amp; extensions, covering Product Knowledge, Refilling, Gel Extension, Tip Application, Acrylic Extension and Remove, over a duration of 2 Months.</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Understand product knowledge. | Learn to refilling. | Practice gel extension. | Explore tip application. | Use basic acrylic extension. | Develop familiarity with remove.</t>
+        </is>
+      </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
@@ -963,17 +979,17 @@
       <c r="R3" s="8" t="n"/>
       <c r="S3" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1011,8 +1027,16 @@
       </c>
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to mehendi design, covering Basic Knowledge, Basic Lines, Humps, Dots, Spiral and Filler Elements, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Understand basic knowledge. | Learn to basic lines. | Practice humps. | Explore dots. | Use basic spiral. | Develop familiarity with filler elements.</t>
+        </is>
+      </c>
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
@@ -1034,17 +1058,17 @@
       <c r="R4" s="8" t="n"/>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1086,8 +1110,16 @@
       </c>
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Fundamentals of Computers, Operating System, MS Office and Internet, over a duration of 120 Hours.</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Understand fundamentals of computers. | Learn to operating system. | Practice ms office. | Explore internet.</t>
+        </is>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
@@ -1109,17 +1141,17 @@
       <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1193,11 @@
       </c>
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Microsoft Office and Internet, over a duration of 120 Hours.</t>
+        </is>
+      </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
@@ -1184,17 +1220,17 @@
       <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1236,8 +1272,16 @@
       </c>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer applications, covering Computer Fundamentals, Operating System, Windows 7, MS Office, Internet &amp; E-Mail and English Typing, over a duration of 1 Year.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to operating system. | Practice windows 7. | Explore ms office. | Use basic internet &amp; e-mail. | Develop familiarity with english typing.</t>
+        </is>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
@@ -1259,17 +1303,17 @@
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1311,8 +1355,16 @@
       </c>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to digital marketing, covering Digital Marketing Concept, Account Management, Campaign &amp; Ad Group Management, Key Targeting, Language &amp; Location Targeting and Budget &amp; Bidding, over a duration of 1 Year.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Understand digital marketing concept. | Learn to account management. | Practice campaign &amp; ad group management. | Explore key targeting. | Use basic language &amp; location targeting. | Develop familiarity with budget &amp; bidding.</t>
+        </is>
+      </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
@@ -1334,17 +1386,17 @@
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1382,14 +1434,22 @@
       </c>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to ai tools &amp; applications, covering Computer Fundamentals, MS Office, Internet, AI Introduction, Chatbots and Content Writers, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore ai introduction. | Use basic chatbots. | Develop familiarity with content writers.</t>
+        </is>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="8" t="inlineStr">
         <is>
-          <t>Computer Fundamentals | MS Office (Word | Excel | PowerPoint) | Internet | AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing</t>
+          <t>Computer Fundamentals | MS Office (Word, Excel, PowerPoint) | Internet | AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr">
@@ -1405,17 +1465,17 @@
       <c r="R9" s="8" t="n"/>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1453,14 +1513,22 @@
       </c>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to ai &amp; digital marketing, covering AI Introduction, Chatbots, Content Writers, Code Generators, Create Images from Text Prompts and Website, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Understand ai introduction. | Learn to chatbots. | Practice content writers. | Explore code generators. | Use basic create images from text prompts. | Develop familiarity with website.</t>
+        </is>
+      </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing | Digital Marketing Introduction | Social Media Marketing (Facebook | Instagram | WhatsApp | Twitter) | Email Marketing | YouTube Content Marketing | Search Engine Optimization (SEO) | Mobile Marketing | Pay-Per-Click | Affiliate Marketing</t>
+          <t>AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing | Digital Marketing Introduction | Social Media Marketing (Facebook, Instagram, WhatsApp, Twitter) | Email Marketing | YouTube Content Marketing | Search Engine Optimization (SEO) | Mobile Marketing | Pay-Per-Click | Affiliate Marketing</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
@@ -1476,17 +1544,17 @@
       <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1524,8 +1592,16 @@
       </c>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to digital marketing, covering Social Media Marketing, Email Marketing, YouTube Content Marketing, Search Engine Optimization, Mobile Marketing and Pay-Per-Click, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Understand social media marketing. | Learn to email marketing. | Practice youtube content marketing. | Explore search engine optimization. | Use basic mobile marketing. | Develop familiarity with pay-per-click.</t>
+        </is>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -1547,17 +1623,17 @@
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1595,8 +1671,16 @@
       </c>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy, covering Computer Fundamentals, MS Office, Internet and PDP, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore pdp.</t>
+        </is>
+      </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
@@ -1618,17 +1702,17 @@
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1666,8 +1750,16 @@
       </c>
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy, covering Fundamentals, Windows, Microsoft Word, Microsoft Excel, Microsoft PowerPoint and Internet, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Understand fundamentals. | Learn to windows. | Practice microsoft word. | Explore microsoft excel. | Use basic microsoft powerpoint. | Develop familiarity with internet.</t>
+        </is>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
@@ -1689,17 +1781,17 @@
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1833,11 @@
       </c>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Assamese Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
@@ -1764,17 +1860,17 @@
       <c r="R14" s="8" t="n"/>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1912,11 @@
       </c>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English &amp; Hindi Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -1839,17 +1939,17 @@
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1991,11 @@
       </c>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Odia Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
@@ -1914,17 +2018,17 @@
       <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2070,11 @@
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English &amp; Bengali Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
@@ -1989,17 +2097,17 @@
       <c r="R17" s="8" t="n"/>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2149,11 @@
       </c>
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Hindi Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
@@ -2064,17 +2176,17 @@
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2228,11 @@
       </c>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Bengali Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
@@ -2139,17 +2255,17 @@
       <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2307,11 @@
       </c>
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
@@ -2214,17 +2334,17 @@
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2386,11 @@
       </c>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -2289,17 +2413,17 @@
       <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2465,11 @@
       </c>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Computer Fundamental and Hindi Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="9" t="n"/>
@@ -2364,17 +2492,17 @@
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2544,11 @@
       </c>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Computer Fundamentals and Bengali Typing using Bijoy &amp; Bengali Word, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
@@ -2439,17 +2571,17 @@
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>mode | level | overview | outcomes | eligibility | certification | fees</t>
+          <t>mode | level | outcomes | eligibility | certification | fees</t>
         </is>
       </c>
     </row>
